--- a/data_u1/studies_2025-04-01_LSR3_H.xlsx
+++ b/data_u1/studies_2025-04-01_LSR3_H.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10608"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sksiafis/Desktop/LSR3_taar1_H_2025.04.01/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sksiafis/Documents/GitHub/LSR3_taar1_H/data_u1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{340FD2D3-951B-D74A-B1B3-985B2B593875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{146BADF0-776F-C641-8D6C-066EC0F894EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="660" yWindow="500" windowWidth="28140" windowHeight="14440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-2760" yWindow="-18920" windowWidth="28140" windowHeight="14440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="258">
   <si>
     <t>Name</t>
   </si>
@@ -317,9 +317,6 @@
     <t>Ulotaront 20-75mg/d; Placebo</t>
   </si>
   <si>
-    <t>Efficacy (acute), safety</t>
-  </si>
-  <si>
     <t>November 21 2016</t>
   </si>
   <si>
@@ -707,9 +704,6 @@
     <t>November 9 2022</t>
   </si>
   <si>
-    <t>November 1 2025</t>
-  </si>
-  <si>
     <t>NCT03669640 (2018)</t>
   </si>
   <si>
@@ -734,9 +728,6 @@
     <t>December 4 2018</t>
   </si>
   <si>
-    <t>May 8 2023</t>
-  </si>
-  <si>
     <t>terminated</t>
   </si>
   <si>
@@ -761,10 +752,61 @@
     <t>October 19 2023</t>
   </si>
   <si>
-    <t>February 8 2026</t>
-  </si>
-  <si>
     <t>Sunovion/Sumitomo; Otsuka</t>
+  </si>
+  <si>
+    <t>NCT06880328 (2019)</t>
+  </si>
+  <si>
+    <t>18F-Dihydroxyphenylalanine (DOPA) Positron Emission Tomography (PET) Study to Explore Dopamine Synthesis Capacity in the Whole Striatum After 2 Weeks of Treatment With Ralmitaront or Placebo in Participants With Schizophrenia</t>
+  </si>
+  <si>
+    <t>BP39833</t>
+  </si>
+  <si>
+    <t>DB-RCT two-period crossover; 2 weeks (phase 1)</t>
+  </si>
+  <si>
+    <t>Ralmitaront 150 mg/d; Placebo</t>
+  </si>
+  <si>
+    <t>F-DOPA PET; fMRI; tolerability</t>
+  </si>
+  <si>
+    <t>September 04 2019</t>
+  </si>
+  <si>
+    <t>November 07 2018</t>
+  </si>
+  <si>
+    <t>February 01 2026</t>
+  </si>
+  <si>
+    <t>February 08 2026</t>
+  </si>
+  <si>
+    <t>May 08 2023</t>
+  </si>
+  <si>
+    <t>NCT06894212 (2025)</t>
+  </si>
+  <si>
+    <t>A Trial of the Efficacy and Safety of SEP-363856 in Acutely Psychotic Participants With Schizophrenia</t>
+  </si>
+  <si>
+    <t>382-201-00035</t>
+  </si>
+  <si>
+    <t>Otsuka</t>
+  </si>
+  <si>
+    <t>Ulotaront 75mg; Ulotaront 100mg; Placebo</t>
+  </si>
+  <si>
+    <t>August 31 2028</t>
+  </si>
+  <si>
+    <t>February 25 2025</t>
   </si>
 </sst>
 </file>
@@ -808,11 +850,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1117,7 +1160,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R27"/>
+  <dimension ref="A1:R29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.1640625" customWidth="1"/>
@@ -1397,7 +1440,7 @@
         <v>58</v>
       </c>
       <c r="D6" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E6" t="s">
         <v>60</v>
@@ -1500,7 +1543,7 @@
         <v>77</v>
       </c>
       <c r="D8" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E8" t="s">
         <v>78</v>
@@ -1547,7 +1590,7 @@
         <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E9" t="s">
         <v>83</v>
@@ -1594,7 +1637,7 @@
         <v>90</v>
       </c>
       <c r="D10" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E10" t="s">
         <v>91</v>
@@ -1609,13 +1652,13 @@
         <v>39</v>
       </c>
       <c r="I10" t="s">
+        <v>50</v>
+      </c>
+      <c r="J10" t="s">
         <v>94</v>
       </c>
-      <c r="J10" t="s">
+      <c r="K10" t="s">
         <v>95</v>
-      </c>
-      <c r="K10" t="s">
-        <v>96</v>
       </c>
       <c r="L10">
         <v>2023</v>
@@ -1630,7 +1673,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q10" t="s">
         <v>55</v>
@@ -1641,25 +1684,25 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>97</v>
+      </c>
+      <c r="B11" t="s">
         <v>98</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>99</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
+        <v>239</v>
+      </c>
+      <c r="E11" t="s">
         <v>100</v>
       </c>
-      <c r="D11" t="s">
-        <v>243</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>101</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>102</v>
-      </c>
-      <c r="G11" t="s">
-        <v>103</v>
       </c>
       <c r="H11">
         <v>463</v>
@@ -1668,10 +1711,10 @@
         <v>50</v>
       </c>
       <c r="J11" t="s">
+        <v>103</v>
+      </c>
+      <c r="K11" t="s">
         <v>104</v>
-      </c>
-      <c r="K11" t="s">
-        <v>105</v>
       </c>
       <c r="L11">
         <v>2023</v>
@@ -1680,7 +1723,7 @@
         <v>25</v>
       </c>
       <c r="N11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O11">
         <v>1</v>
@@ -1697,25 +1740,25 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>106</v>
+      </c>
+      <c r="B12" t="s">
         <v>107</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>108</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
+        <v>239</v>
+      </c>
+      <c r="E12" t="s">
         <v>109</v>
       </c>
-      <c r="D12" t="s">
-        <v>243</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>110</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>111</v>
-      </c>
-      <c r="G12" t="s">
-        <v>112</v>
       </c>
       <c r="H12">
         <v>245</v>
@@ -1724,10 +1767,10 @@
         <v>50</v>
       </c>
       <c r="J12" t="s">
+        <v>112</v>
+      </c>
+      <c r="K12" t="s">
         <v>113</v>
-      </c>
-      <c r="K12" t="s">
-        <v>114</v>
       </c>
       <c r="L12">
         <v>2018</v>
@@ -1753,37 +1796,37 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
+        <v>114</v>
+      </c>
+      <c r="B13" t="s">
         <v>115</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>116</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
+        <v>239</v>
+      </c>
+      <c r="E13" t="s">
         <v>117</v>
       </c>
-      <c r="D13" t="s">
-        <v>243</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>118</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>119</v>
-      </c>
-      <c r="G13" t="s">
-        <v>120</v>
       </c>
       <c r="H13">
         <v>105</v>
       </c>
       <c r="I13" t="s">
+        <v>120</v>
+      </c>
+      <c r="J13" t="s">
         <v>121</v>
       </c>
-      <c r="J13" t="s">
+      <c r="K13" t="s">
         <v>122</v>
-      </c>
-      <c r="K13" t="s">
-        <v>123</v>
       </c>
       <c r="L13">
         <v>2015</v>
@@ -1792,7 +1835,7 @@
         <v>25</v>
       </c>
       <c r="N13" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="O13">
         <v>1</v>
@@ -1806,25 +1849,25 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>124</v>
+      </c>
+      <c r="B14" t="s">
         <v>125</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>126</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
+        <v>239</v>
+      </c>
+      <c r="E14" t="s">
         <v>127</v>
       </c>
-      <c r="D14" t="s">
-        <v>243</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>128</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>129</v>
-      </c>
-      <c r="G14" t="s">
-        <v>130</v>
       </c>
       <c r="H14">
         <v>48</v>
@@ -1833,10 +1876,10 @@
         <v>24</v>
       </c>
       <c r="J14" t="s">
+        <v>130</v>
+      </c>
+      <c r="K14" t="s">
         <v>131</v>
-      </c>
-      <c r="K14" t="s">
-        <v>132</v>
       </c>
       <c r="L14">
         <v>2014</v>
@@ -1862,37 +1905,37 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>132</v>
+      </c>
+      <c r="B15" t="s">
         <v>133</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>134</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
+        <v>239</v>
+      </c>
+      <c r="E15" t="s">
         <v>135</v>
       </c>
-      <c r="D15" t="s">
-        <v>243</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>136</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>137</v>
-      </c>
-      <c r="G15" t="s">
-        <v>138</v>
       </c>
       <c r="H15">
         <v>18</v>
       </c>
       <c r="I15" t="s">
+        <v>138</v>
+      </c>
+      <c r="J15" t="s">
         <v>139</v>
       </c>
-      <c r="J15" t="s">
+      <c r="K15" t="s">
         <v>140</v>
-      </c>
-      <c r="K15" t="s">
-        <v>141</v>
       </c>
       <c r="L15">
         <v>2015</v>
@@ -1907,7 +1950,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="R15">
         <v>18</v>
@@ -1915,25 +1958,25 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>142</v>
+      </c>
+      <c r="B16" t="s">
         <v>143</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>144</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
+        <v>239</v>
+      </c>
+      <c r="E16" t="s">
         <v>145</v>
       </c>
-      <c r="D16" t="s">
-        <v>243</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>146</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>147</v>
-      </c>
-      <c r="G16" t="s">
-        <v>148</v>
       </c>
       <c r="H16">
         <v>48</v>
@@ -1942,10 +1985,10 @@
         <v>24</v>
       </c>
       <c r="J16" t="s">
+        <v>148</v>
+      </c>
+      <c r="K16" t="s">
         <v>149</v>
-      </c>
-      <c r="K16" t="s">
-        <v>150</v>
       </c>
       <c r="L16">
         <v>2014</v>
@@ -1971,25 +2014,25 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
+        <v>150</v>
+      </c>
+      <c r="B17" t="s">
         <v>151</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>152</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
+        <v>239</v>
+      </c>
+      <c r="E17" t="s">
+        <v>100</v>
+      </c>
+      <c r="F17" t="s">
         <v>153</v>
       </c>
-      <c r="D17" t="s">
-        <v>243</v>
-      </c>
-      <c r="E17" t="s">
-        <v>101</v>
-      </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>154</v>
-      </c>
-      <c r="G17" t="s">
-        <v>155</v>
       </c>
       <c r="H17">
         <v>462</v>
@@ -1998,10 +2041,10 @@
         <v>50</v>
       </c>
       <c r="J17" t="s">
+        <v>155</v>
+      </c>
+      <c r="K17" t="s">
         <v>156</v>
-      </c>
-      <c r="K17" t="s">
-        <v>157</v>
       </c>
       <c r="L17">
         <v>2023</v>
@@ -2010,7 +2053,7 @@
         <v>25</v>
       </c>
       <c r="N17" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O17">
         <v>1</v>
@@ -2027,25 +2070,25 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
+        <v>157</v>
+      </c>
+      <c r="B18" t="s">
         <v>158</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>159</v>
-      </c>
-      <c r="C18" t="s">
-        <v>160</v>
       </c>
       <c r="D18" t="s">
         <v>59</v>
       </c>
       <c r="E18" t="s">
+        <v>160</v>
+      </c>
+      <c r="F18" t="s">
         <v>161</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>162</v>
-      </c>
-      <c r="G18" t="s">
-        <v>163</v>
       </c>
       <c r="H18">
         <v>13</v>
@@ -2054,10 +2097,10 @@
         <v>24</v>
       </c>
       <c r="J18" t="s">
+        <v>163</v>
+      </c>
+      <c r="K18" t="s">
         <v>164</v>
-      </c>
-      <c r="K18" t="s">
-        <v>165</v>
       </c>
       <c r="L18">
         <v>2020</v>
@@ -2083,37 +2126,37 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
+        <v>165</v>
+      </c>
+      <c r="B19" t="s">
         <v>166</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>167</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
+        <v>239</v>
+      </c>
+      <c r="E19" t="s">
         <v>168</v>
       </c>
-      <c r="D19" t="s">
-        <v>243</v>
-      </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
+        <v>161</v>
+      </c>
+      <c r="G19" t="s">
         <v>169</v>
-      </c>
-      <c r="F19" t="s">
-        <v>162</v>
-      </c>
-      <c r="G19" t="s">
-        <v>170</v>
       </c>
       <c r="H19">
         <v>68</v>
       </c>
       <c r="I19" t="s">
+        <v>170</v>
+      </c>
+      <c r="J19" t="s">
         <v>171</v>
       </c>
-      <c r="J19" t="s">
+      <c r="K19" t="s">
         <v>172</v>
-      </c>
-      <c r="K19" t="s">
-        <v>173</v>
       </c>
       <c r="L19">
         <v>2020</v>
@@ -2139,37 +2182,37 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
+        <v>173</v>
+      </c>
+      <c r="B20" t="s">
         <v>174</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>175</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
+        <v>239</v>
+      </c>
+      <c r="E20" t="s">
         <v>176</v>
       </c>
-      <c r="D20" t="s">
-        <v>243</v>
-      </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
+        <v>161</v>
+      </c>
+      <c r="G20" t="s">
         <v>177</v>
-      </c>
-      <c r="F20" t="s">
-        <v>162</v>
-      </c>
-      <c r="G20" t="s">
-        <v>178</v>
       </c>
       <c r="H20">
         <v>60</v>
       </c>
       <c r="I20" t="s">
+        <v>178</v>
+      </c>
+      <c r="J20" t="s">
         <v>179</v>
       </c>
-      <c r="J20" t="s">
+      <c r="K20" t="s">
         <v>180</v>
-      </c>
-      <c r="K20" t="s">
-        <v>181</v>
       </c>
       <c r="L20">
         <v>2024</v>
@@ -2195,37 +2238,37 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
+        <v>181</v>
+      </c>
+      <c r="B21" t="s">
         <v>182</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>183</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
+        <v>239</v>
+      </c>
+      <c r="E21" t="s">
         <v>184</v>
       </c>
-      <c r="D21" t="s">
-        <v>243</v>
-      </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
+        <v>161</v>
+      </c>
+      <c r="G21" t="s">
         <v>185</v>
-      </c>
-      <c r="F21" t="s">
-        <v>162</v>
-      </c>
-      <c r="G21" t="s">
-        <v>186</v>
       </c>
       <c r="H21">
         <v>302</v>
       </c>
       <c r="I21" t="s">
+        <v>186</v>
+      </c>
+      <c r="J21" t="s">
         <v>187</v>
       </c>
-      <c r="J21" t="s">
+      <c r="K21" t="s">
         <v>188</v>
-      </c>
-      <c r="K21" t="s">
-        <v>189</v>
       </c>
       <c r="L21">
         <v>2022</v>
@@ -2251,37 +2294,37 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
+        <v>189</v>
+      </c>
+      <c r="B22" t="s">
         <v>190</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>191</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
+        <v>239</v>
+      </c>
+      <c r="E22" t="s">
         <v>192</v>
       </c>
-      <c r="D22" t="s">
-        <v>243</v>
-      </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>193</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>194</v>
-      </c>
-      <c r="G22" t="s">
-        <v>195</v>
       </c>
       <c r="H22">
         <v>19</v>
       </c>
       <c r="I22" t="s">
+        <v>195</v>
+      </c>
+      <c r="J22" t="s">
         <v>196</v>
       </c>
-      <c r="J22" t="s">
+      <c r="K22" t="s">
         <v>197</v>
-      </c>
-      <c r="K22" t="s">
-        <v>198</v>
       </c>
       <c r="L22">
         <v>2024</v>
@@ -2307,37 +2350,37 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
+        <v>198</v>
+      </c>
+      <c r="B23" t="s">
         <v>199</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>200</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
+        <v>239</v>
+      </c>
+      <c r="E23" t="s">
         <v>201</v>
       </c>
-      <c r="D23" t="s">
-        <v>243</v>
-      </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
+        <v>193</v>
+      </c>
+      <c r="G23" t="s">
         <v>202</v>
-      </c>
-      <c r="F23" t="s">
-        <v>194</v>
-      </c>
-      <c r="G23" t="s">
-        <v>203</v>
       </c>
       <c r="H23">
         <v>31</v>
       </c>
       <c r="I23" t="s">
+        <v>203</v>
+      </c>
+      <c r="J23" t="s">
         <v>204</v>
       </c>
-      <c r="J23" t="s">
+      <c r="K23" t="s">
         <v>205</v>
-      </c>
-      <c r="K23" t="s">
-        <v>206</v>
       </c>
       <c r="L23">
         <v>2023</v>
@@ -2346,7 +2389,7 @@
         <v>25</v>
       </c>
       <c r="N23" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O23">
         <v>1</v>
@@ -2363,40 +2406,40 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
+        <v>207</v>
+      </c>
+      <c r="B24" t="s">
         <v>208</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>209</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
+        <v>239</v>
+      </c>
+      <c r="E24" t="s">
         <v>210</v>
       </c>
-      <c r="D24" t="s">
-        <v>243</v>
-      </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>211</v>
       </c>
-      <c r="F24" t="s">
-        <v>212</v>
-      </c>
       <c r="G24" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H24">
         <v>464</v>
       </c>
       <c r="I24" t="s">
+        <v>212</v>
+      </c>
+      <c r="J24" t="s">
         <v>213</v>
       </c>
-      <c r="J24" t="s">
+      <c r="K24" t="s">
+        <v>249</v>
+      </c>
+      <c r="M24" t="s">
         <v>214</v>
-      </c>
-      <c r="K24" t="s">
-        <v>242</v>
-      </c>
-      <c r="M24" t="s">
-        <v>215</v>
       </c>
       <c r="N24" t="s">
         <v>26</v>
@@ -2405,7 +2448,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="Q24" t="s">
         <v>55</v>
@@ -2416,40 +2459,40 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
+        <v>215</v>
+      </c>
+      <c r="B25" t="s">
         <v>216</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>217</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
+        <v>239</v>
+      </c>
+      <c r="E25" t="s">
         <v>218</v>
       </c>
-      <c r="D25" t="s">
-        <v>243</v>
-      </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>219</v>
       </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
         <v>220</v>
-      </c>
-      <c r="G25" t="s">
-        <v>221</v>
       </c>
       <c r="H25">
         <v>1030</v>
       </c>
       <c r="I25" t="s">
+        <v>221</v>
+      </c>
+      <c r="J25" t="s">
         <v>222</v>
       </c>
-      <c r="J25" t="s">
-        <v>223</v>
-      </c>
-      <c r="K25" t="s">
-        <v>224</v>
+      <c r="K25" s="2" t="s">
+        <v>248</v>
       </c>
       <c r="M25" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="N25" t="s">
         <v>26</v>
@@ -2458,7 +2501,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="Q25" t="s">
         <v>55</v>
@@ -2469,43 +2512,43 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
+        <v>223</v>
+      </c>
+      <c r="B26" t="s">
+        <v>224</v>
+      </c>
+      <c r="C26" t="s">
         <v>225</v>
-      </c>
-      <c r="B26" t="s">
-        <v>226</v>
-      </c>
-      <c r="C26" t="s">
-        <v>227</v>
       </c>
       <c r="D26" t="s">
         <v>20</v>
       </c>
       <c r="E26" t="s">
+        <v>226</v>
+      </c>
+      <c r="F26" t="s">
+        <v>227</v>
+      </c>
+      <c r="G26" t="s">
         <v>228</v>
-      </c>
-      <c r="F26" t="s">
-        <v>229</v>
-      </c>
-      <c r="G26" t="s">
-        <v>230</v>
       </c>
       <c r="H26">
         <v>131</v>
       </c>
       <c r="I26" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="J26" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="K26" t="s">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="L26">
         <v>2023</v>
       </c>
       <c r="M26" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="N26" t="s">
         <v>53</v>
@@ -2517,7 +2560,7 @@
         <v>54</v>
       </c>
       <c r="Q26" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="R26">
         <v>131</v>
@@ -2525,25 +2568,25 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B27" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C27" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D27" t="s">
         <v>59</v>
       </c>
       <c r="E27" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="F27" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G27" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H27">
         <v>83</v>
@@ -2552,16 +2595,16 @@
         <v>50</v>
       </c>
       <c r="J27" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="K27" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="L27">
         <v>2023</v>
       </c>
       <c r="M27" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="N27" t="s">
         <v>26</v>
@@ -2577,6 +2620,115 @@
       </c>
       <c r="R27">
         <v>83</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>240</v>
+      </c>
+      <c r="B28" t="s">
+        <v>241</v>
+      </c>
+      <c r="C28" t="s">
+        <v>242</v>
+      </c>
+      <c r="D28" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" t="s">
+        <v>243</v>
+      </c>
+      <c r="F28" t="s">
+        <v>161</v>
+      </c>
+      <c r="G28" t="s">
+        <v>244</v>
+      </c>
+      <c r="H28">
+        <v>35</v>
+      </c>
+      <c r="I28" t="s">
+        <v>245</v>
+      </c>
+      <c r="J28" t="s">
+        <v>247</v>
+      </c>
+      <c r="K28" t="s">
+        <v>246</v>
+      </c>
+      <c r="L28">
+        <v>2019</v>
+      </c>
+      <c r="M28" t="s">
+        <v>25</v>
+      </c>
+      <c r="N28" t="s">
+        <v>26</v>
+      </c>
+      <c r="O28">
+        <v>1</v>
+      </c>
+      <c r="P28" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>67</v>
+      </c>
+      <c r="R28">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>251</v>
+      </c>
+      <c r="B29" t="s">
+        <v>252</v>
+      </c>
+      <c r="C29" t="s">
+        <v>253</v>
+      </c>
+      <c r="D29" t="s">
+        <v>254</v>
+      </c>
+      <c r="E29" t="s">
+        <v>100</v>
+      </c>
+      <c r="F29" t="s">
+        <v>153</v>
+      </c>
+      <c r="G29" t="s">
+        <v>255</v>
+      </c>
+      <c r="H29">
+        <v>522</v>
+      </c>
+      <c r="I29" t="s">
+        <v>50</v>
+      </c>
+      <c r="J29" t="s">
+        <v>257</v>
+      </c>
+      <c r="K29" t="s">
+        <v>256</v>
+      </c>
+      <c r="M29" t="s">
+        <v>214</v>
+      </c>
+      <c r="N29" t="s">
+        <v>26</v>
+      </c>
+      <c r="O29">
+        <v>1</v>
+      </c>
+      <c r="P29" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>55</v>
+      </c>
+      <c r="R29">
+        <v>522</v>
       </c>
     </row>
   </sheetData>
